--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1675,6 +1675,87 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>D20260914M06</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1724,7 +1805,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1744,7 +1825,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,11 +812,11 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -893,11 +893,11 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -974,11 +974,11 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-3.55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.74%</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32.25</v>
+        <v>32.04</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>7000</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-2.13%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -831,7 +831,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-3.12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-2.03%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -831,7 +831,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1.94%</t>
+          <t>-2.38%</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>-1.81%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5.07%</t>
+          <t>-6.13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>-1.57%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.81%</t>
+          <t>-2.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,11 +1055,11 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,11 +1217,11 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.63%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>+1.98%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>+4.19%</t>
+          <t>+4.25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5.85%</t>
+          <t>-4.99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>+3.64%</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-0.71%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,11 +1055,11 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>待观察</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>+4.25%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>已验证</t>
+          <t>待观察</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,11 +1217,11 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>待观察</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>已验证</t>
+          <t>待观察</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-2.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,11 +1055,11 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,11 +1217,11 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-4.99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1697,60 +1697,141 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32.04</v>
+        <v>32.25</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>D20260916M04</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>31.53</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -1794,7 +1875,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1886,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1815,7 +1896,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1825,7 +1906,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1835,7 +1916,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -1846,7 +1927,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1939,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-0.71%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,11 +1136,11 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-10.08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,11 +1298,11 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+1.39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1379,11 +1379,11 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1460,11 +1460,11 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1541,11 +1541,11 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+1.10%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>-1.04%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10.08%</t>
+          <t>-9.44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-8.51%</t>
+          <t>-7.50%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>+2.97%</t>
+          <t>+3.55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>+1.10%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>-3.26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-0.96%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1837,6 +1837,249 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>D2026091701</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M01</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>中国平安(601318)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>D20260917M03</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1886,7 +2129,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -1906,7 +2149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-8.33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,11 +1622,11 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>-1.45%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.74%</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>-5.85%</t>
+          <t>-5.82%</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-4.92%</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-8.33%</t>
+          <t>-8.36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2075,6 +2075,87 @@
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>D2026091801</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>11800</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2129,7 +2210,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2149,7 +2230,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2182,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-1.42%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2105,7 +2105,7 @@
         <v>31.41</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>11800</v>
+        <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,11 +1703,11 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-3.22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.12%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>+4.04%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.11%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-6.61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-1.40%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -821,7 +821,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-6.61%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-6.34%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3.23%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.00%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+5.87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,11 +1784,11 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-1.40%</t>
+          <t>-0.86%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+2.08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-7.00%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>+5.87%</t>
+          <t>+6.03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>+0.91%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+1.21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>-0.84%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-11.46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-3.41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-3.78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,11 +1865,11 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -1946,11 +1946,11 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2027,11 +2027,11 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.78%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11.46%</t>
+          <t>-12.05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-9.41%</t>
+          <t>-9.64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-3.41%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3.78%</t>
+          <t>-4.11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>+1.74%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-2.40%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-2.54%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>+2.41%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1950,24 +1950,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>-0.54%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>-0.47%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>-0.11%</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>+1.65%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,11 +2108,11 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.00%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.72%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7.59%</t>
+          <t>-6.93%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>-3.76%</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+3.17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7.00%</t>
+          <t>-6.34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-3.70%</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2158,6 +2158,87 @@
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>已验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>D2026092801</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>沪深300ETF(510300)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>258900</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2291,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2230,7 +2311,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-8.37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+5.53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-0.54%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2242,168 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>D2026092901</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>28300</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>D2026092902</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代(300750)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2291,7 +2453,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -2311,7 +2473,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1712,7 +1712,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-8.37%</t>
+          <t>-8.65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+5.64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-0.44%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1793,7 +1793,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7.04%</t>
+          <t>-6.85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>-3.91%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.62%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1874,7 +1874,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.81%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-10.25%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.81%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.45%</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-9.13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.81%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.96%</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2189,11 +2189,11 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-0.72%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-5.59%</t>
+          <t>-5.55%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-5.81%</t>
+          <t>-5.72%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-10.25%</t>
+          <t>-9.39%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-5.81%</t>
+          <t>-5.72%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>-4.45%</t>
+          <t>-3.67%</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9.13%</t>
+          <t>-8.59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-5.81%</t>
+          <t>-5.72%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-2.87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4.71%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>-4.96%</t>
+          <t>-4.87%</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1.34%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-0.67%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,26 +2270,26 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>+2.88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2351,26 +2351,26 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>+0.80%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.60%</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.40%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-0.49%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-6.92%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.79%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-10.49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.79%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.70%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.79%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>-0.57%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6.92%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-6.79%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-10.49%</t>
+          <t>-11.17%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-6.79%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>-3.70%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8.45%</t>
+          <t>-8.71%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-6.79%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2401,6 +2401,87 @@
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>已验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D2026101401</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>中国平安(601318)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>18200</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2534,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2473,7 +2554,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2506,7 +2587,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.56%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+5.86%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.55%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+15.41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-13.11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.55%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>-0.17%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+6.33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-9.55%</t>
+          <t>-8.89%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>+15.41%</t>
+          <t>+15.22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-13.11%</t>
+          <t>-13.23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-9.55%</t>
+          <t>-8.89%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>+4.34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2480,6 +2480,87 @@
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>D2026101501</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>长江电力(600900)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>29000</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2534,7 +2615,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2554,7 +2635,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2587,7 +2668,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-12.22%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.95%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+4.46%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.95%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+12.41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.95%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+6.42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-1.90%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.95%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6.04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.95%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-12.11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.21%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12.22%</t>
+          <t>-12.31%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-7.95%</t>
+          <t>-8.31%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>-4.28%</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>+4.46%</t>
+          <t>+4.89%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-7.95%</t>
+          <t>-8.31%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>+12.41%</t>
+          <t>+13.20%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-7.95%</t>
+          <t>-8.31%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>+6.42%</t>
+          <t>+6.84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1.90%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-7.95%</t>
+          <t>-8.31%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>-6.04%</t>
+          <t>-6.46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>+4.59%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-7.95%</t>
+          <t>-8.31%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>-12.11%</t>
+          <t>-12.90%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.20%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-6.36%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.67%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>-4.23%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t>-1.22%</t>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.07%</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.21%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6.36%</t>
+          <t>-5.76%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-7.67%</t>
+          <t>-7.44%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>-4.07%</t>
+          <t>-3.83%</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2561,6 +2561,87 @@
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>D2026101901</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代(300750)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>267.02</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2615,7 +2696,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -2635,7 +2716,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2668,7 +2749,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.22%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-10.91%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7.79%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2279,14 +2279,14 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>-2.77%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
           <t>-1.60%</t>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.92%</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2360,14 +2360,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>-10.18%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
           <t>-1.60%</t>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.92%</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.21%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-10.91%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-7.79%</t>
+          <t>-7.32%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>+2.57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2.77%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>+2.15%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-10.18%</t>
+          <t>-9.67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-4.44%</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-5.22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2642,6 +2642,87 @@
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>D2026102001</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>美的集团(000333)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2696,7 +2777,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2716,7 +2797,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,26 +2432,26 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.23%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2436,7 +2436,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.24%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-11.99%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.94%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,26 +2513,26 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>+0.64%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+3.79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.14%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11.99%</t>
+          <t>-11.70%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-9.94%</t>
+          <t>-9.91%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>+3.79%</t>
+          <t>+3.86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2723,6 +2723,87 @@
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>D2026102201</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>紫金矿业(601899)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>38600</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2777,7 +2858,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2797,7 +2878,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2830,7 +2911,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.85%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-4.00%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.85%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-7.01%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8.85%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-7.73%</t>
+          <t>-6.83%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-8.85%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>-1.12%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4.00%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-8.85%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-7.01%</t>
+          <t>-6.10%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-8.85%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2804,6 +2804,87 @@
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>D2026102301</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代(300750)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>237.6</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
@@ -2858,7 +2939,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2878,7 +2959,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2911,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.25%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>-12.70%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-9.26%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,26 +2594,26 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>-10.01%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+7.99%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>4500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.18%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2122,7 +2122,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-12.70%</t>
+          <t>-12.54%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-9.26%</t>
+          <t>-8.96%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>-3.58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-10.01%</t>
+          <t>-10.87%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2.02%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>+9.17%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.17%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,26 +2675,26 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>4500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.13%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2679,7 +2679,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>+0.70%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>+1.52%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>-2.51%</t>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>4500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.20%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2441,7 +2441,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>+1.52%</t>
+          <t>+2.11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-3.17%</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-5.28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2522,14 +2522,14 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>-3.11%</t>
@@ -2537,14 +2537,14 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>-3.07%</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>+3.86%</t>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+4.15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2756,56 +2756,56 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>+0.14%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
         <v>4500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.14%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2522,7 +2522,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>+4.15%</t>
+          <t>+4.30%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2760,24 +2760,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>+0.72%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待观察</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
           <t>+0.14%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>+0.04%</t>
-        </is>
-      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>—</t>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.15%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -569,7 +569,7 @@
         <v>259900</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         <v>35900</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>20600</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>258900</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>36500</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>21200</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>13500</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>16700</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>18200</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>4500</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>5000</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>9200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>8700</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>7000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>14000</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>6300</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>3000</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>6000</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>10300</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>258900</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>28300</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>1100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>18200</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>29000</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>1100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>4500</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>38600</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2837,56 +2837,56 @@
         <v>4500</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>-1.78%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>待观察</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>待观察</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
+          <t>-2.82%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>待观察</t>
+          <t>已验证</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.13%</t>
         </is>
       </c>
     </row>

--- a/outputs/19_决策后验证.xlsx
+++ b/outputs/19_决策后验证.xlsx
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
